--- a/18-companion-data-model.xlsx
+++ b/18-companion-data-model.xlsx
@@ -1667,9 +1667,10 @@
         <f>(B13+B22)/B21</f>
         <v/>
       </c>
-      <c r="C26" s="15">
-        <f> (capital+financing + electricity) / annual tokens (millions)</f>
-        <v/>
+      <c r="C26" s="15" t="inlineStr">
+        <is>
+          <t>(capital+financing + electricity) / annual tokens (millions)</t>
+        </is>
       </c>
     </row>
     <row r="28">
@@ -3010,9 +3011,10 @@
         <f>(B18+B20+B21)/B22</f>
         <v/>
       </c>
-      <c r="C25" s="34">
-        <f> (financed capital + electricity + opex) / annual tokens (millions) — this is the paper's canonical Hyperscale figure</f>
-        <v/>
+      <c r="C25" s="34" t="inlineStr">
+        <is>
+          <t>(financed capital + electricity + opex) / annual tokens (millions) — this is the paper's canonical Hyperscale figure</t>
+        </is>
       </c>
     </row>
     <row r="27">
